--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/report-controller/getMemberProgressReport-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/report-controller/getMemberProgressReport-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="99">
-  <si>
-    <t>Statement: report-controller.getMemberProgressReport(memberId, startDate, endDate) – Server Action. Validates via memberProgressReportSchema (memberId non-empty, startDate/endDate in YYYY-MM-DD format). Delegates to reportService.getMemberProgressReport(). Returns ActionResult&lt;Report&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="146">
+  <si>
+    <t>Statement: getMemberProgressReport(memberId, startDate, endDate) – Validates the input parameters and returns an ActionResult&lt;Report&gt;. Returns success with the generated report on success. memberId must be a non-empty, non-whitespace-only string; surrounding whitespace is trimmed before validation. startDate and endDate must be present and in YYYY-MM-DD format. A report with no sessions in range returns zero-valued aggregates. Exercise breakdown is sorted by totalVolume descending. Returns a field-level validation error for schema failures without calling the service. Returns a failure with the service error message for NotFoundError. Returns a failure with message "An unexpected error occurred" for any other unexpected error.</t>
   </si>
   <si>
     <t/>
@@ -37,21 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>reportService.getMemberProgressReport is mock-injected</t>
+    <t>memberId: non-empty, non-whitespace-only string (trimmed before validation). startDate and endDate: YYYY-MM-DD format, both required. startDate equal to endDate is accepted (single-day range).</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;Report&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;Report&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: Report returned.
-On validation failure: errors returned.
-On AppError: message returned.</t>
+    <t>On success: report generated successfully, returned data contains memberId, aggregated stats, exerciseBreakdown sorted by totalVolume descending, and sessionDetails. On validation failure: field-level validation error returned, the service is not called. On NotFoundError: operation fails with the service error message. On unexpected error: operation fails with message "An unexpected error occurred".</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,37 +64,73 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>memberId</t>
-  </si>
-  <si>
-    <t>non-empty string</t>
-  </si>
-  <si>
-    <t>empty memberId → validation error</t>
-  </si>
-  <si>
-    <t>startDate</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD format</t>
-  </si>
-  <si>
-    <t>invalid date format → validation error</t>
-  </si>
-  <si>
-    <t>endDate</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves Report</t>
-  </si>
-  <si>
-    <t>throws NotFoundError → failure</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All fields valid → report generated successfully, returned data contains memberId, exerciseBreakdown (length 1) and sessionDetails (length 1)</t>
+  </si>
+  <si>
+    <t>Session count</t>
+  </si>
+  <si>
+    <t>No sessions in the date range → report generated successfully with totalSessions: 0, totalVolume: 0, averageSessionDuration: 0, exerciseBreakdown empty</t>
+  </si>
+  <si>
+    <t>Two sessions in the date range → report generated successfully with totalSessions: 2, correct averageSessionDuration and totalVolume</t>
+  </si>
+  <si>
+    <t>Exercise count</t>
+  </si>
+  <si>
+    <t>Two distinct exercises → report generated successfully with exerciseBreakdown length 2 and correct per-exercise aggregates</t>
+  </si>
+  <si>
+    <t>Exercise sort order</t>
+  </si>
+  <si>
+    <t>Multiple exercises → exerciseBreakdown sorted by totalVolume descending (highest first)</t>
+  </si>
+  <si>
+    <t>memberId required</t>
+  </si>
+  <si>
+    <t>memberId: undefined → validation fails: memberId field error returned</t>
+  </si>
+  <si>
+    <t>startDate required</t>
+  </si>
+  <si>
+    <t>startDate: undefined → validation fails: startDate field error returned</t>
+  </si>
+  <si>
+    <t>endDate required</t>
+  </si>
+  <si>
+    <t>endDate: undefined → validation fails: endDate field error returned</t>
+  </si>
+  <si>
+    <t>startDate format</t>
+  </si>
+  <si>
+    <t>startDate: "2024.01.01" (invalid format) → validation fails: startDate field error returned</t>
+  </si>
+  <si>
+    <t>endDate format</t>
+  </si>
+  <si>
+    <t>endDate: "12/31/2024" (invalid format) → validation fails: endDate field error returned</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>Member does not exist (NotFoundError "Member not found") → operation fails with message "Member not found"</t>
+  </si>
+  <si>
+    <t>Error type</t>
+  </si>
+  <si>
+    <t>Unexpected error occurs → operation fails with message "An unexpected error occurred"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -114,64 +148,109 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,3,5,7</t>
-  </si>
-  <si>
-    <t>memberId="member-001", startDate="2024-01-01", endDate="2024-03-31", service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true, data: Report }</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>memberId="", startDate="2024-01-01", endDate="2024-03-31"</t>
-  </si>
-  <si>
-    <t>{ success: false, errors.memberId defined }</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>memberId="member-001", startDate="not-a-date", endDate="2024-03-31"</t>
-  </si>
-  <si>
-    <t>{ success: false, errors.startDate defined }</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>memberId="member-001", startDate="2024-01-01", endDate="not-a-date"</t>
-  </si>
-  <si>
-    <t>{ success: false, errors.endDate defined }</t>
-  </si>
-  <si>
-    <t>memberId="member-001", startDate="01/01/2024", endDate="31-03-2024"</t>
-  </si>
-  <si>
-    <t>{ success: false, errors defined }</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>valid input, service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Member not found" }</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>valid input, service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>all fields valid (memberId, startDate "2024-01-01", endDate "2024-12-31"), report is generated successfully with one exercise and one session</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data memberId matches, exerciseBreakdown has length 1 and sessionDetails has length 1</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>all fields valid, no sessions exist in the date range, report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully with totalSessions: 0, totalVolume: 0, averageSessionDuration: 0, exerciseBreakdown empty</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>all fields valid, two sessions exist in the date range (durationMinutes 60 and 90), report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data totalSessions is 2, averageSessionDuration is 75, totalVolume is 3000</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>all fields valid, two distinct exercises exist in the breakdown (Bench Press and Squat), report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully, exerciseBreakdown has length 2, second exercise name is "Squat"</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>all fields valid, two exercises with totalVolume 10000 ("ex-high") and 1000 ("ex-low"), report is generated successfully with exerciseBreakdown sorted descending</t>
+  </si>
+  <si>
+    <t>report generated successfully, exerciseBreakdown[0].totalVolume is greater than exerciseBreakdown[1].totalVolume, exerciseBreakdown[0].exerciseId is "ex-high"</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>memberId: undefined, startDate "2024-01-01", endDate "2024-12-31"</t>
+  </si>
+  <si>
+    <t>validation fails: memberId field error returned</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>valid memberId, startDate: undefined, endDate "2024-12-31"</t>
+  </si>
+  <si>
+    <t>validation fails: startDate field error returned</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>valid memberId, startDate "2024-01-01", endDate: undefined</t>
+  </si>
+  <si>
+    <t>validation fails: endDate field error returned</t>
+  </si>
+  <si>
+    <t>EC-9</t>
+  </si>
+  <si>
+    <t>valid memberId, startDate: "2024.01.01" (dot-separated, invalid format), endDate "2024-12-31"</t>
+  </si>
+  <si>
+    <t>EC-10</t>
+  </si>
+  <si>
+    <t>valid memberId, startDate "2024-01-01", endDate: "12/31/2024" (MM/DD/YYYY, invalid format)</t>
+  </si>
+  <si>
+    <t>EC-11</t>
+  </si>
+  <si>
+    <t>all fields valid, member does not exist (NotFoundError "Member not found")</t>
+  </si>
+  <si>
+    <t>operation fails with message "Member not found"</t>
+  </si>
+  <si>
+    <t>EC-12</t>
+  </si>
+  <si>
+    <t>all fields valid, an unexpected error occurs during report generation</t>
+  </si>
+  <si>
+    <t>operation fails with message "An unexpected error occurred"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -183,31 +262,127 @@
     <t>memberId length</t>
   </si>
   <si>
-    <t>memberId="" (empty) → invalid</t>
-  </si>
-  <si>
-    <t>memberId="m" (1 char) → valid (non-empty)</t>
+    <t>memberId: "" (length 0): empty → validation fails: memberId field error returned</t>
+  </si>
+  <si>
+    <t>memberId: "A" (length 1, min): shortest valid id → report generated successfully, returned data memberId is "A"</t>
+  </si>
+  <si>
+    <t>memberId: "AB" (length 2, min + 1): above minimum → report generated successfully, returned data memberId is "AB"</t>
+  </si>
+  <si>
+    <t>memberId content</t>
+  </si>
+  <si>
+    <t>memberId: "   " (whitespace-only): empty after trim → validation fails: memberId field error returned</t>
+  </si>
+  <si>
+    <t>memberId trim</t>
+  </si>
+  <si>
+    <t>memberId: "  member-uuid-001  " (surrounding whitespace): trimmed before validation → report generated successfully, returned data memberId is "member-uuid-001"</t>
+  </si>
+  <si>
+    <t>date range boundary</t>
+  </si>
+  <si>
+    <t>startDate === endDate ("2024-06-15"): single-day range → report generated successfully, returned data startDate and endDate are both 2024-06-15</t>
+  </si>
+  <si>
+    <t>exercise weight</t>
+  </si>
+  <si>
+    <t>one exercise with weight: 0 → report generated successfully, returned data totalVolume is 0 and exerciseBreakdown[0].totalVolume is 0</t>
+  </si>
+  <si>
+    <t>exercise reps</t>
+  </si>
+  <si>
+    <t>one exercise with reps: 0 → report generated successfully, returned data totalVolume is 0</t>
+  </si>
+  <si>
+    <t>session duration</t>
+  </si>
+  <si>
+    <t>one session with durationMinutes: 0 → report generated successfully, returned data averageSessionDuration is 0</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>memberId empty</t>
-  </si>
-  <si>
-    <t>memberId=""</t>
-  </si>
-  <si>
-    <t>success=false, errors.memberId defined</t>
-  </si>
-  <si>
-    <t>memberId 1 char</t>
-  </si>
-  <si>
-    <t>memberId="m"</t>
-  </si>
-  <si>
-    <t>schema passes (non-empty satisfied)</t>
+    <t>BVA-1 (memberId=0)</t>
+  </si>
+  <si>
+    <t>memberId: "" (empty string), startDate "2024-01-01", endDate "2024-12-31"</t>
+  </si>
+  <si>
+    <t>BVA-2 (memberId=1)</t>
+  </si>
+  <si>
+    <t>memberId: "A" (1 character), startDate "2024-01-01", endDate "2024-12-31", report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data memberId is "A"</t>
+  </si>
+  <si>
+    <t>BVA-3 (memberId=2)</t>
+  </si>
+  <si>
+    <t>memberId: "AB" (2 characters), startDate "2024-01-01", endDate "2024-12-31", report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data memberId is "AB"</t>
+  </si>
+  <si>
+    <t>BVA-4 (memberId=ws)</t>
+  </si>
+  <si>
+    <t>memberId: "   " (whitespace-only), startDate "2024-01-01", endDate "2024-12-31"</t>
+  </si>
+  <si>
+    <t>BVA-5 (memberId=trim)</t>
+  </si>
+  <si>
+    <t>memberId: "  member-uuid-001  " (surrounding whitespace), startDate "2024-01-01", endDate "2024-12-31", report is generated successfully after trimming</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data memberId is "member-uuid-001"</t>
+  </si>
+  <si>
+    <t>BVA-6 (same date)</t>
+  </si>
+  <si>
+    <t>memberId valid, startDate: "2024-06-15", endDate: "2024-06-15" (same date, single-day range), report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data startDate and endDate are both the 2024-06-15 Date</t>
+  </si>
+  <si>
+    <t>BVA-7 (weight=0)</t>
+  </si>
+  <si>
+    <t>all fields valid, one exercise with weight: 0 in session details, report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data totalVolume is 0 and exerciseBreakdown[0].totalVolume is 0</t>
+  </si>
+  <si>
+    <t>BVA-8 (reps=0)</t>
+  </si>
+  <si>
+    <t>all fields valid, one exercise with reps: 0 in session details, report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data totalVolume is 0</t>
+  </si>
+  <si>
+    <t>BVA-9 (duration=0)</t>
+  </si>
+  <si>
+    <t>all fields valid, one session with durationMinutes: 0, report is generated successfully</t>
+  </si>
+  <si>
+    <t>report generated successfully, returned data averageSessionDuration is 0</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -216,64 +391,31 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
+    <t>BVA-1</t>
   </si>
   <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>Valid memberId and dates, service resolves</t>
-  </si>
-  <si>
-    <t>success=true, Report returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>Empty memberId</t>
-  </si>
-  <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Invalid startDate format</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Invalid endDate format</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Both dates non-ISO format</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
-    <t>Service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-7</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
   </si>
   <si>
     <t>Testing</t>
@@ -306,16 +448,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>RPG-01</t>
+    <t>CTRL-28</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -831,7 +970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -872,13 +1011,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -886,7 +1025,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>19</v>
@@ -900,13 +1039,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -914,10 +1053,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1</v>
@@ -928,13 +1067,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -942,13 +1081,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -956,13 +1095,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,13 +1109,55 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -987,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -999,19 +1180,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1019,16 +1200,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1036,16 +1217,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1053,16 +1234,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1070,16 +1251,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1087,16 +1268,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1104,16 +1285,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1121,16 +1302,101 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1141,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1151,13 +1417,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1165,21 +1431,98 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1533,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1202,19 +1545,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1222,16 +1565,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1239,16 +1582,135 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>62</v>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1259,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1272,22 +1734,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1295,19 +1757,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1315,19 +1777,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1335,19 +1797,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1355,19 +1817,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1375,19 +1837,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1395,19 +1857,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,19 +1877,299 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>84</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1455,16 +2197,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1472,45 +2214,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>95</v>
+      <c r="A3" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="B3" s="1">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1519,19 +2261,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>98</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
